--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -662,12 +662,11 @@
           <t>NSE:SIEMENS26SEP4100CE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-27 10:04:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -662,11 +662,7 @@
           <t>NSE:SIEMENS26SEP4100CE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2026-08-27 10:04:00</t>
-        </is>
-      </c>
+      <c r="AC2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -662,7 +662,11 @@
           <t>NSE:SIEMENS26SEP4100CE</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-27 10:14:58</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +667,190 @@
           <t>2026-08-27 10:14:58</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-27 10:57:25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>108.54</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="H3" t="n">
+        <v>110</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12406</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="T3" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="U3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:VMM26SEP110PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-27 10:57:25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1039.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1040</v>
+      </c>
+      <c r="I4" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="K4" t="n">
+        <v>38.12</v>
+      </c>
+      <c r="L4" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="M4" t="n">
+        <v>47.66</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1597</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="S4" t="n">
+        <v>22</v>
+      </c>
+      <c r="T4" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="U4" t="n">
+        <v>28</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:HINDALCO26SEP1040CE</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -756,6 +756,11 @@
           <t>NSE:VMM26SEP110PE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-27 10:59:01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -845,12 +850,11 @@
           <t>NSE:HINDALCO26SEP1040CE</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-27 10:59:01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,6 +855,101 @@
           <t>2026-08-27 10:59:01</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:11:36</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H5" t="n">
+        <v>385</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="K5" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5434</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>48.51</v>
+      </c>
+      <c r="U5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:INDUSTOWER26SEP385PE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -944,12 +944,11 @@
           <t>NSE:INDUSTOWER26SEP385PE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:13:11</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -944,11 +944,7 @@
           <t>NSE:INDUSTOWER26SEP385PE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-08-27 11:13:11</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -944,7 +944,11 @@
           <t>NSE:INDUSTOWER26SEP385PE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:28:51</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -944,11 +944,7 @@
           <t>NSE:INDUSTOWER26SEP385PE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-08-27 11:28:51</t>
-        </is>
-      </c>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,7 +944,101 @@
           <t>NSE:INDUSTOWER26SEP385PE</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:41:25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>424.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H6" t="n">
+        <v>425</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>5464</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="U6" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:KOTAKBANK26SEP425CE</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -944,6 +944,11 @@
           <t>NSE:INDUSTOWER26SEP385PE</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-27 11:43:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1033,12 +1038,6 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1038,6 +1038,11 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-27 12:58:31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1038,11 +1038,7 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-27 12:58:31</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1038,7 +1038,101 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:14:14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>622.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H7" t="n">
+        <v>620</v>
+      </c>
+      <c r="I7" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="K7" t="n">
+        <v>33.93</v>
+      </c>
+      <c r="L7" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="M7" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1709</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="S7" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="U7" t="n">
+        <v>29</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26SEP620CE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1127,12 +1127,100 @@
           <t>NSE:KALYANKJIL26SEP620CE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:17:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:17:33</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>887.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H8" t="n">
+        <v>880</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2409</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="T8" t="n">
+        <v>53.45</v>
+      </c>
+      <c r="U8" t="n">
+        <v>18</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:CGPOWER26SEP880PE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1127,6 +1127,16 @@
           <t>NSE:KALYANKJIL26SEP620CE</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:22:17</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-27 13:17:33</t>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1132,9 +1132,14 @@
           <t>2026-08-27 13:22:17</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:27:03</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,6 +944,16 @@
           <t>NSE:INDUSTOWER26SEP385PE</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:47:36</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>2026-08-27 11:43:00</t>
@@ -1236,6 +1246,101 @@
           <t>NSE:CGPOWER26SEP880PE</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:47:40</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>391.05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2.07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>390</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="L9" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="M9" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3278</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="S9" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="U9" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:NATIONALUM26SEP390CE</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -850,6 +850,16 @@
           <t>NSE:HINDALCO26SEP1040CE</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:48:35</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2026-08-27 10:59:01</t>
@@ -1335,12 +1345,6 @@
           <t>NSE:NATIONALUM26SEP390CE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1058,6 +1058,11 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:55:40</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1058,11 +1058,7 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-27 13:55:40</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1058,7 +1058,6 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1255,6 +1254,11 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:CGPOWER26SEP880PE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:21:54</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1256,11 +1256,7 @@
           <t>NSE:CGPOWER26SEP880PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-27 14:21:54</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,7 +1256,6 @@
           <t>NSE:CGPOWER26SEP880PE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1346,6 +1345,101 @@
           <t>NSE:NATIONALUM26SEP390CE</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:36:30</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>713.05</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="H10" t="n">
+        <v>710</v>
+      </c>
+      <c r="I10" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="K10" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="L10" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4310</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="S10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="U10" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:HDFCBANK26SEP710PE</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1434,12 +1434,11 @@
           <t>NSE:HDFCBANK26SEP710PE</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:38:06</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1434,11 +1434,7 @@
           <t>NSE:HDFCBANK26SEP710PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-27 14:38:06</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1434,7 +1434,11 @@
           <t>NSE:HDFCBANK26SEP710PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:42:54</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1256,6 +1256,21 @@
           <t>NSE:CGPOWER26SEP880PE</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:45:57</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:46:05</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1058,6 +1058,11 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:52:34</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1360,6 +1365,11 @@
           <t>NSE:NATIONALUM26SEP390CE</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:52:34</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1449,9 +1459,182 @@
           <t>NSE:HDFCBANK26SEP710PE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-27 14:42:54</t>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:52:34</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VMM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>107.57</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1.87</v>
+      </c>
+      <c r="H11" t="n">
+        <v>110</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12406</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="S11" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="U11" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:VMM26SEP110PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:52:34</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>4402.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4400</v>
+      </c>
+      <c r="I12" t="n">
+        <v>156</v>
+      </c>
+      <c r="J12" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>190.15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>210.65</v>
+      </c>
+      <c r="M12" t="n">
+        <v>237.97</v>
+      </c>
+      <c r="N12" t="n">
+        <v>320</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="S12" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>55.52</v>
+      </c>
+      <c r="U12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:GVT&amp;D26SEP4400PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1058,11 +1058,6 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-27 14:52:34</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1365,11 +1360,6 @@
           <t>NSE:NATIONALUM26SEP390CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-27 14:52:34</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1459,6 +1449,11 @@
           <t>NSE:HDFCBANK26SEP710PE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:53:25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1548,6 +1543,11 @@
           <t>NSE:VMM26SEP110PE</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:53:26</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1635,6 +1635,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:GVT&amp;D26SEP4400PE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:53:25</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1642,6 +1642,101 @@
           <t>2026-08-27 14:53:25</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:55:02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1921.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I13" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="J13" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="K13" t="n">
+        <v>51.31</v>
+      </c>
+      <c r="L13" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="M13" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1254</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="S13" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>63.14</v>
+      </c>
+      <c r="U13" t="n">
+        <v>43</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:LAURUSLABS26SEP1920CE</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1731,12 +1731,11 @@
           <t>NSE:LAURUSLABS26SEP1920CE</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-27 14:56:48</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1543,11 +1543,7 @@
           <t>NSE:VMM26SEP110PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-08-27 14:53:26</t>
-        </is>
-      </c>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1058,6 +1058,11 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-27 15:00:01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1543,7 +1548,11 @@
           <t>NSE:VMM26SEP110PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-27 15:00:02</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1725,11 +1734,6 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:LAURUSLABS26SEP1920CE</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-08-27 14:56:48</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1058,11 +1058,7 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-27 15:00:01</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1058,7 +1058,11 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-27 15:12:10</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1548,11 +1548,7 @@
           <t>NSE:VMM26SEP110PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-08-27 15:00:02</t>
-        </is>
-      </c>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1548,7 +1548,11 @@
           <t>NSE:VMM26SEP110PE</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-27 15:29:40</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1730,6 +1734,95 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:LAURUSLABS26SEP1920CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-27 15:29:40</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>711</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.23</v>
+      </c>
+      <c r="H14" t="n">
+        <v>710</v>
+      </c>
+      <c r="I14" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="K14" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4310</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="S14" t="n">
+        <v>19</v>
+      </c>
+      <c r="T14" t="n">
+        <v>28.26</v>
+      </c>
+      <c r="U14" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:HDFCBANK26SEP710PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -1825,6 +1825,16 @@
           <t>NSE:HDFCBANK26SEP710PE</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-27 15:31:16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
+++ b/backend/signal_logs/2026-08-27/signals_2026-08-27.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:SIEMENS26SEP4100CE</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Closed flat ~135.0 (+0.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>2026-08-27 10:14:58</t>
@@ -756,6 +761,11 @@
           <t>NSE:VMM26SEP110PE</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Closed up ~4.1 (+1.7% from entry)</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>2026-08-27 10:59:01</t>
@@ -1058,6 +1068,11 @@
           <t>NSE:KOTAKBANK26SEP425CE</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Closed down ~8.95 (-2.2% from entry)</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026-08-27 15:12:10</t>
@@ -1365,6 +1380,11 @@
           <t>NSE:NATIONALUM26SEP390CE</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Closed down ~14.25 (-6.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1454,6 +1474,16 @@
           <t>NSE:HDFCBANK26SEP710PE</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-27 15:30:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>2026-08-27 14:53:25</t>
@@ -1548,6 +1578,11 @@
           <t>NSE:VMM26SEP110PE</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Closed up ~4.32 (+7.2% from entry)</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-08-27 15:29:40</t>
@@ -1642,6 +1677,11 @@
           <t>NSE:GVT&amp;D26SEP4400PE</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Closed up ~161.3 (+3.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-27 14:53:25</t>
@@ -1734,6 +1774,11 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>NSE:LAURUSLABS26SEP1920CE</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed down ~38.5 (-3.4% from entry, EOD estimate)</t>
         </is>
       </c>
     </row>
